--- a/Feature Analysis.xlsx
+++ b/Feature Analysis.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Thesis V2X\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Thesis V2X\Project on Git\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C590044-BA6D-420F-AB51-BC9B8A5E1E26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A480F75F-E6B7-4F24-AE43-207C1D83DBCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{70500DC6-AD36-4B09-A399-63EA8DBC8070}"/>
   </bookViews>
@@ -1599,7 +1599,7 @@
         <v>18</v>
       </c>
       <c r="D16" s="5"/>
-      <c r="E16" s="26"/>
+      <c r="E16" s="1"/>
       <c r="F16" s="1"/>
       <c r="G16" s="1"/>
       <c r="H16" s="1"/>
@@ -1886,8 +1886,8 @@
       <c r="C34" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="D34" s="5"/>
-      <c r="E34" s="1"/>
+      <c r="D34" s="26"/>
+      <c r="E34" s="6"/>
       <c r="F34" s="1"/>
       <c r="G34" s="1"/>
       <c r="H34" s="1"/>
@@ -1902,8 +1902,8 @@
       <c r="C35" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="D35" s="5"/>
-      <c r="E35" s="1"/>
+      <c r="D35" s="26"/>
+      <c r="E35" s="6"/>
       <c r="F35" s="1"/>
       <c r="G35" s="1"/>
       <c r="H35" s="1"/>
@@ -1934,8 +1934,8 @@
       <c r="C37" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="D37" s="5"/>
-      <c r="E37" s="1"/>
+      <c r="D37" s="26"/>
+      <c r="E37" s="6"/>
       <c r="F37" s="1"/>
       <c r="G37" s="1"/>
       <c r="H37" s="1"/>
@@ -1950,8 +1950,8 @@
       <c r="C38" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="D38" s="5"/>
-      <c r="E38" s="1"/>
+      <c r="D38" s="26"/>
+      <c r="E38" s="6"/>
       <c r="F38" s="1"/>
       <c r="G38" s="1"/>
       <c r="H38" s="1"/>
@@ -1982,8 +1982,8 @@
       <c r="C40" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="D40" s="5"/>
-      <c r="E40" s="1"/>
+      <c r="D40" s="26"/>
+      <c r="E40" s="6"/>
       <c r="F40" s="1"/>
       <c r="G40" s="1"/>
       <c r="H40" s="1"/>
@@ -1998,8 +1998,8 @@
       <c r="C41" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="D41" s="5"/>
-      <c r="E41" s="1"/>
+      <c r="D41" s="26"/>
+      <c r="E41" s="6"/>
       <c r="F41" s="1"/>
       <c r="G41" s="1"/>
       <c r="H41" s="1"/>
@@ -2894,7 +2894,7 @@
       <c r="C97" s="16" t="s">
         <v>99</v>
       </c>
-      <c r="D97" s="26"/>
+      <c r="D97" s="1"/>
       <c r="E97" s="1"/>
       <c r="F97" s="19"/>
       <c r="G97" s="1"/>
@@ -2910,7 +2910,7 @@
       <c r="C98" s="16" t="s">
         <v>100</v>
       </c>
-      <c r="D98" s="26"/>
+      <c r="D98" s="1"/>
       <c r="E98" s="1"/>
       <c r="F98" s="19"/>
       <c r="G98" s="1"/>
@@ -2926,7 +2926,7 @@
       <c r="C99" s="16" t="s">
         <v>101</v>
       </c>
-      <c r="D99" s="26"/>
+      <c r="D99" s="1"/>
       <c r="E99" s="1"/>
       <c r="F99" s="19"/>
       <c r="G99" s="1"/>
@@ -2942,7 +2942,7 @@
       <c r="C100" s="16" t="s">
         <v>102</v>
       </c>
-      <c r="D100" s="26"/>
+      <c r="D100" s="1"/>
       <c r="E100" s="1"/>
       <c r="F100" s="19"/>
       <c r="G100" s="1"/>
@@ -2958,7 +2958,7 @@
       <c r="C101" s="16" t="s">
         <v>103</v>
       </c>
-      <c r="D101" s="26"/>
+      <c r="D101" s="1"/>
       <c r="E101" s="1"/>
       <c r="F101" s="19"/>
       <c r="G101" s="1"/>
@@ -2974,7 +2974,7 @@
       <c r="C102" s="16" t="s">
         <v>104</v>
       </c>
-      <c r="D102" s="26"/>
+      <c r="D102" s="1"/>
       <c r="E102" s="1"/>
       <c r="F102" s="19"/>
       <c r="G102" s="1"/>
@@ -2990,7 +2990,7 @@
       <c r="C103" s="16" t="s">
         <v>105</v>
       </c>
-      <c r="D103" s="26"/>
+      <c r="D103" s="1"/>
       <c r="E103" s="1"/>
       <c r="F103" s="19"/>
       <c r="G103" s="1"/>
@@ -3006,7 +3006,7 @@
       <c r="C104" s="16" t="s">
         <v>106</v>
       </c>
-      <c r="D104" s="26"/>
+      <c r="D104" s="1"/>
       <c r="E104" s="1"/>
       <c r="F104" s="19"/>
       <c r="G104" s="1"/>
@@ -3022,7 +3022,7 @@
       <c r="C105" s="16" t="s">
         <v>107</v>
       </c>
-      <c r="D105" s="26"/>
+      <c r="D105" s="1"/>
       <c r="E105" s="1"/>
       <c r="F105" s="19"/>
       <c r="G105" s="1"/>
@@ -3038,7 +3038,7 @@
       <c r="C106" s="16" t="s">
         <v>108</v>
       </c>
-      <c r="D106" s="26"/>
+      <c r="D106" s="1"/>
       <c r="E106" s="1"/>
       <c r="F106" s="19"/>
       <c r="G106" s="1"/>
@@ -3054,7 +3054,7 @@
       <c r="C107" s="16" t="s">
         <v>109</v>
       </c>
-      <c r="D107" s="26"/>
+      <c r="D107" s="1"/>
       <c r="E107" s="1"/>
       <c r="F107" s="19"/>
       <c r="G107" s="1"/>
@@ -3070,7 +3070,7 @@
       <c r="C108" s="16" t="s">
         <v>110</v>
       </c>
-      <c r="D108" s="26"/>
+      <c r="D108" s="1"/>
       <c r="E108" s="1"/>
       <c r="F108" s="19"/>
       <c r="G108" s="1"/>
@@ -3086,7 +3086,7 @@
       <c r="C109" s="16" t="s">
         <v>111</v>
       </c>
-      <c r="D109" s="26"/>
+      <c r="D109" s="1"/>
       <c r="E109" s="1"/>
       <c r="F109" s="19"/>
       <c r="G109" s="7"/>
@@ -3102,7 +3102,7 @@
       <c r="C110" s="16" t="s">
         <v>112</v>
       </c>
-      <c r="D110" s="26"/>
+      <c r="D110" s="1"/>
       <c r="E110" s="1"/>
       <c r="F110" s="19"/>
       <c r="G110" s="7"/>
@@ -3630,7 +3630,7 @@
       <c r="C143" s="16" t="s">
         <v>145</v>
       </c>
-      <c r="D143" s="26"/>
+      <c r="D143" s="1"/>
       <c r="E143" s="1"/>
       <c r="F143" s="19"/>
       <c r="G143" s="7"/>
@@ -3646,7 +3646,7 @@
       <c r="C144" s="21" t="s">
         <v>146</v>
       </c>
-      <c r="D144" s="26"/>
+      <c r="D144" s="1"/>
       <c r="E144" s="1"/>
       <c r="F144" s="19"/>
       <c r="G144" s="7"/>
@@ -3662,7 +3662,7 @@
       <c r="C145" s="21" t="s">
         <v>147</v>
       </c>
-      <c r="D145" s="26"/>
+      <c r="D145" s="1"/>
       <c r="E145" s="1"/>
       <c r="F145" s="19"/>
       <c r="G145" s="7"/>
@@ -3678,7 +3678,7 @@
       <c r="C146" s="21" t="s">
         <v>148</v>
       </c>
-      <c r="D146" s="26"/>
+      <c r="D146" s="1"/>
       <c r="E146" s="1"/>
       <c r="F146" s="19"/>
       <c r="G146" s="7"/>
@@ -3694,7 +3694,7 @@
       <c r="C147" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="D147" s="26"/>
+      <c r="D147" s="1"/>
       <c r="E147" s="1"/>
       <c r="F147" s="19"/>
       <c r="G147" s="7"/>
@@ -3710,7 +3710,7 @@
       <c r="C148" s="16" t="s">
         <v>150</v>
       </c>
-      <c r="D148" s="26"/>
+      <c r="D148" s="1"/>
       <c r="E148" s="1"/>
       <c r="F148" s="19"/>
       <c r="G148" s="7"/>
@@ -3726,7 +3726,7 @@
       <c r="C149" s="16" t="s">
         <v>151</v>
       </c>
-      <c r="D149" s="26"/>
+      <c r="D149" s="1"/>
       <c r="E149" s="1"/>
       <c r="F149" s="19"/>
       <c r="G149" s="7"/>
@@ -3742,7 +3742,7 @@
       <c r="C150" s="16" t="s">
         <v>152</v>
       </c>
-      <c r="D150" s="26"/>
+      <c r="D150" s="1"/>
       <c r="E150" s="1"/>
       <c r="F150" s="19"/>
       <c r="G150" s="7"/>
@@ -3758,7 +3758,7 @@
       <c r="C151" s="16" t="s">
         <v>153</v>
       </c>
-      <c r="D151" s="26"/>
+      <c r="D151" s="1"/>
       <c r="E151" s="1"/>
       <c r="F151" s="19"/>
       <c r="G151" s="7"/>
